--- a/Result/profitability/2912.xlsx
+++ b/Result/profitability/2912.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.92</v>
       </c>
       <c r="M2" t="n">
-        <v>2.465</v>
+        <v>2.4875</v>
       </c>
       <c r="N2" t="n">
-        <v>33.81</v>
+        <v>33.87625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.19</v>
       </c>
       <c r="M3" t="n">
-        <v>2.255</v>
+        <v>2.365</v>
       </c>
       <c r="N3" t="n">
-        <v>33.57375</v>
+        <v>33.59875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.13375</v>
+        <v>2.16625</v>
       </c>
       <c r="N4" t="n">
-        <v>33.0925</v>
+        <v>33.1725</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>1.85125</v>
+        <v>1.86625</v>
       </c>
       <c r="N5" t="n">
-        <v>33.23625</v>
+        <v>33.25625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.84</v>
       </c>
       <c r="M6" t="n">
-        <v>1.59</v>
+        <v>1.615</v>
       </c>
       <c r="N6" t="n">
-        <v>32.905</v>
+        <v>32.8525</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.13</v>
       </c>
       <c r="M7" t="n">
-        <v>1.375</v>
+        <v>1.47875</v>
       </c>
       <c r="N7" t="n">
-        <v>32.6475</v>
+        <v>32.71250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2725</v>
+        <v>1.2825</v>
       </c>
       <c r="N8" t="n">
-        <v>32.395</v>
+        <v>32.39625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.63</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9799999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="N9" t="n">
         <v>32.20625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>92176</v>
+      </c>
+      <c r="D75" t="n">
+        <v>60295</v>
+      </c>
+      <c r="E75" t="n">
+        <v>31881</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3845</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>862</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4708</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3174</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.73125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.385</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07999999999999963</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02693602693602681</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.01000000000000512</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0002891844997110482</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1199999999999997</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.04095563139931735</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1600000000000037</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.004647110078420003</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
